--- a/data/CoreShell_Simulation_Input.xlsx
+++ b/data/CoreShell_Simulation_Input.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Uni\Programming\SasRMC\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B68D21-9901-40B4-9B02-F64C87CA5F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571E6E46-E40C-461C-B842-10F96E588AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Simulation parameters" sheetId="1" r:id="rId1"/>
@@ -584,15 +579,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.53125" customWidth="1"/>
+    <col min="3" max="3" width="17.86328125" customWidth="1"/>
+    <col min="8" max="8" width="21.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>62</v>
       </c>
@@ -600,7 +595,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -611,12 +606,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -624,7 +619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -632,7 +627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -640,7 +635,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -648,7 +643,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -656,7 +651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -664,7 +659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -672,7 +667,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -680,7 +675,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -688,7 +683,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -699,7 +694,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -710,7 +705,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -718,7 +713,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -726,7 +721,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -737,7 +732,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -748,7 +743,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -759,7 +754,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -767,7 +762,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -778,7 +773,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -789,7 +784,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -800,27 +795,27 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -828,7 +823,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -836,7 +831,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -844,7 +839,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>22</v>
       </c>
@@ -852,7 +847,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -860,7 +855,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -868,7 +863,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -876,7 +871,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -884,7 +879,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -892,7 +887,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -900,7 +895,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -908,32 +903,32 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>67</v>
       </c>
@@ -941,7 +936,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -949,7 +944,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -959,28 +954,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BDDED57-5B0F-428D-B84D-2EAB6C58DB05}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.86328125" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.46484375" customWidth="1"/>
     <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.1328125" customWidth="1"/>
     <col min="8" max="8" width="17.33203125" customWidth="1"/>
     <col min="9" max="9" width="23.33203125" customWidth="1"/>
-    <col min="10" max="10" width="23.109375" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.1328125" customWidth="1"/>
+    <col min="11" max="11" width="15.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>66</v>
       </c>
@@ -1017,14 +1013,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4FEA4A-6BE6-4B62-BCAA-5DB3A0F42670}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>